--- a/AAAGameData/DataTables/Level/LevelTable.xlsx
+++ b/AAAGameData/DataTables/Level/LevelTable.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="152">
   <si>
     <t>#</t>
   </si>
@@ -978,154 +978,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" applyFont="1" fillId="6" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="8" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="9" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="12" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="14" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="16" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="18" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="20" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="22" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="24" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="26" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="28" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="30" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="32" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="33" applyFill="1" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1474,7 +1474,7 @@
     <col min="37" max="38" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" customHeight="1">
+    <row r="1" ht="14.75" customHeight="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" ht="28.75" customHeight="1">
+    <row r="2" ht="28.75" customHeight="1" spans="1:38">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" ht="28.75" customHeight="1">
+    <row r="3" ht="28.75" customHeight="1" spans="1:38">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" ht="13" customHeight="1">
+    <row r="4" ht="13" customHeight="1" spans="1:38">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1868,1210 +1868,1210 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" ht="42.75" customHeight="1">
-      <c r="B5" s="0">
+    <row r="5" ht="42.75" customHeight="1" spans="1:38">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" t="s">
         <v>87</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" t="s">
         <v>88</v>
       </c>
-      <c r="K5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="M5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R5" s="0">
-        <v>0</v>
-      </c>
-      <c r="S5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U5" s="0">
-        <v>0</v>
-      </c>
-      <c r="V5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X5" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA5" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD5" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="0">
+      <c r="K5" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" t="s">
+        <v>4</v>
+      </c>
+      <c r="P5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>4</v>
+      </c>
+      <c r="T5" t="s">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>4</v>
+      </c>
+      <c r="W5" t="s">
+        <v>4</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>50</v>
       </c>
-      <c r="AF5" s="0">
+      <c r="AF5">
         <v>20</v>
       </c>
-      <c r="AG5" s="0">
+      <c r="AG5">
         <v>40</v>
       </c>
-      <c r="AH5" s="0">
+      <c r="AH5">
         <v>15</v>
       </c>
-      <c r="AI5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ5" s="0" t="s">
+      <c r="AI5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>89</v>
       </c>
-      <c r="AK5" s="0" t="s">
+      <c r="AK5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" ht="70.75" customHeight="1">
-      <c r="B6" s="0">
+    <row r="6" ht="70.75" customHeight="1" spans="1:38">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>4</v>
+      </c>
+      <c r="O6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>99</v>
+      </c>
+      <c r="R6">
+        <v>15</v>
+      </c>
+      <c r="S6" t="s">
+        <v>100</v>
+      </c>
+      <c r="T6" t="s">
+        <v>4</v>
+      </c>
+      <c r="U6">
+        <v>10</v>
+      </c>
+      <c r="V6" t="s">
+        <v>4</v>
+      </c>
+      <c r="W6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>50</v>
+      </c>
+      <c r="AF6">
+        <v>20</v>
+      </c>
+      <c r="AG6">
+        <v>40</v>
+      </c>
+      <c r="AH6">
+        <v>15</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" ht="70.75" customHeight="1" spans="1:38">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" t="s">
+        <v>96</v>
+      </c>
+      <c r="K7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" t="s">
+        <v>97</v>
+      </c>
+      <c r="M7" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R7">
+        <v>15</v>
+      </c>
+      <c r="S7" t="s">
+        <v>98</v>
+      </c>
+      <c r="T7" t="s">
+        <v>99</v>
+      </c>
+      <c r="U7">
+        <v>20</v>
+      </c>
+      <c r="V7" t="s">
+        <v>4</v>
+      </c>
+      <c r="W7" t="s">
+        <v>4</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>50</v>
+      </c>
+      <c r="AF7">
+        <v>20</v>
+      </c>
+      <c r="AG7">
+        <v>40</v>
+      </c>
+      <c r="AH7">
+        <v>15</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" ht="42.75" customHeight="1" spans="1:38">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
+        <v>4</v>
+      </c>
+      <c r="W8" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>50</v>
+      </c>
+      <c r="AF8">
+        <v>20</v>
+      </c>
+      <c r="AG8">
+        <v>40</v>
+      </c>
+      <c r="AH8">
+        <v>15</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75" customHeight="1" spans="1:38">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>4</v>
+      </c>
+      <c r="W9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>50</v>
+      </c>
+      <c r="AF9">
+        <v>20</v>
+      </c>
+      <c r="AG9">
+        <v>40</v>
+      </c>
+      <c r="AH9">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" ht="42.75" customHeight="1" spans="1:38">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
+        <v>4</v>
+      </c>
+      <c r="W10" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>50</v>
+      </c>
+      <c r="AF10">
+        <v>20</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" ht="42.75" customHeight="1" spans="1:38">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" t="s">
+        <v>97</v>
+      </c>
+      <c r="M11" t="s">
+        <v>4</v>
+      </c>
+      <c r="N11" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" t="s">
+        <v>4</v>
+      </c>
+      <c r="P11" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>4</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
+        <v>4</v>
+      </c>
+      <c r="T11" t="s">
+        <v>4</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
+        <v>4</v>
+      </c>
+      <c r="W11" t="s">
+        <v>4</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>50</v>
+      </c>
+      <c r="AF11">
+        <v>20</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" ht="56.75" customHeight="1" spans="1:38">
+      <c r="B12">
         <v>8</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="D12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" t="s">
+        <v>135</v>
+      </c>
+      <c r="G12" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
+        <v>4</v>
+      </c>
+      <c r="T12" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
+        <v>4</v>
+      </c>
+      <c r="W12" t="s">
+        <v>4</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>50</v>
+      </c>
+      <c r="AF12">
+        <v>20</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:38">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J13" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N13" t="s">
+        <v>4</v>
+      </c>
+      <c r="O13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>4</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>4</v>
+      </c>
+      <c r="T13" t="s">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>4</v>
+      </c>
+      <c r="W13" t="s">
+        <v>4</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>50</v>
+      </c>
+      <c r="AF13">
+        <v>20</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" ht="42.75" customHeight="1" spans="1:38">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14" t="s">
+        <v>121</v>
+      </c>
+      <c r="J14" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>4</v>
+      </c>
+      <c r="W14" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>50</v>
+      </c>
+      <c r="AF14">
+        <v>20</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" ht="70.75" customHeight="1" spans="1:38">
+      <c r="B15">
+        <v>1000</v>
+      </c>
+      <c r="C15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15">
+        <v>200</v>
+      </c>
+      <c r="I15" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J15" t="s">
         <v>96</v>
       </c>
-      <c r="K6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="0" t="s">
+      <c r="K15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" t="s">
         <v>97</v>
       </c>
-      <c r="M6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P6" s="0" t="s">
+      <c r="M15" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" t="s">
         <v>98</v>
       </c>
-      <c r="Q6" s="0" t="s">
+      <c r="Q15" t="s">
         <v>99</v>
       </c>
-      <c r="R6" s="0">
-        <v>15</v>
-      </c>
-      <c r="S6" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="T6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U6" s="0">
+      <c r="R15">
         <v>10</v>
       </c>
-      <c r="V6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X6" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA6" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD6" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF6" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG6" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH6" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI6" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ6" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK6" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="AL6" s="0" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" ht="70.75" customHeight="1">
-      <c r="B7" s="0">
-        <v>3</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="H7" s="0">
-        <v>9</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P7" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q7" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="R7" s="0">
-        <v>15</v>
-      </c>
-      <c r="S7" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="T7" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="U7" s="0">
-        <v>20</v>
-      </c>
-      <c r="V7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X7" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF7" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG7" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH7" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ7" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="AK7" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL7" s="0" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" ht="42.75" customHeight="1">
-      <c r="B8" s="0">
-        <v>4</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="H8" s="0">
-        <v>6</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="0">
-        <v>0</v>
-      </c>
-      <c r="S8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="0">
-        <v>0</v>
-      </c>
-      <c r="V8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF8" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG8" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH8" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK8" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL8" s="0" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" ht="42.75" customHeight="1">
-      <c r="B9" s="0">
-        <v>5</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="H9" s="0">
-        <v>6</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R9" s="0">
-        <v>0</v>
-      </c>
-      <c r="S9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U9" s="0">
-        <v>0</v>
-      </c>
-      <c r="V9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X9" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF9" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG9" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH9" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ9" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK9" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="AL9" s="0" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" customHeight="1">
-      <c r="B10" s="0">
-        <v>6</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="H10" s="0">
-        <v>6</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R10" s="0">
-        <v>0</v>
-      </c>
-      <c r="S10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U10" s="0">
-        <v>0</v>
-      </c>
-      <c r="V10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X10" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF10" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK10" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL10" s="0" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" ht="42.75" customHeight="1">
-      <c r="B11" s="0">
-        <v>7</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="0">
-        <v>6</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="J11" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R11" s="0">
-        <v>0</v>
-      </c>
-      <c r="S11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U11" s="0">
-        <v>0</v>
-      </c>
-      <c r="V11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X11" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF11" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK11" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL11" s="0" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" ht="56.75" customHeight="1">
-      <c r="B12" s="0">
-        <v>8</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="H12" s="0">
-        <v>6</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R12" s="0">
-        <v>0</v>
-      </c>
-      <c r="S12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U12" s="0">
-        <v>0</v>
-      </c>
-      <c r="V12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X12" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF12" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK12" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL12" s="0" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="B13" s="0">
-        <v>9</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="H13" s="0">
-        <v>6</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R13" s="0">
-        <v>0</v>
-      </c>
-      <c r="S13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U13" s="0">
-        <v>0</v>
-      </c>
-      <c r="V13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X13" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF13" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK13" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="AL13" s="0" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" ht="42.75" customHeight="1">
-      <c r="B14" s="0">
-        <v>10</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="H14" s="0">
-        <v>6</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="0">
-        <v>0</v>
-      </c>
-      <c r="S14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="0">
-        <v>0</v>
-      </c>
-      <c r="V14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X14" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF14" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL14" s="0" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" ht="70.75" customHeight="1">
-      <c r="B15" s="0">
-        <v>1000</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="H15" s="0">
-        <v>200</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="J15" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="M15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q15" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="R15" s="0">
-        <v>10</v>
-      </c>
-      <c r="S15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="0">
-        <v>0</v>
-      </c>
-      <c r="V15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL15" s="0" t="s">
+      <c r="S15" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL15" t="s">
         <v>127</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Level/LevelTable.xlsx
+++ b/AAAGameData/DataTables/Level/LevelTable.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="154">
   <si>
     <t>#</t>
   </si>
@@ -984,154 +984,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" applyFont="1" fillId="6" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="8" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="9" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="12" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="14" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="16" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="18" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="20" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="22" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="24" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="26" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="28" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="30" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="32" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="33" applyFill="1" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1480,7 +1480,7 @@
     <col min="37" max="38" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" customHeight="1">
+    <row r="1" ht="14.75" customHeight="1" spans="1:39">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="28.75" customHeight="1">
+    <row r="2" ht="28.75" customHeight="1" spans="1:39">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" ht="28.75" customHeight="1">
+    <row r="3" ht="28.75" customHeight="1" spans="1:39">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" ht="13" customHeight="1">
+    <row r="4" ht="13" customHeight="1" spans="1:39">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1886,1243 +1886,1243 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" ht="42.75" customHeight="1">
-      <c r="B5" s="0">
+    <row r="5" ht="42.75" customHeight="1" spans="1:39">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" t="s">
         <v>88</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" t="s">
         <v>89</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" t="s">
         <v>90</v>
       </c>
-      <c r="K5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R5" s="0">
-        <v>0</v>
-      </c>
-      <c r="S5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U5" s="0">
-        <v>0</v>
-      </c>
-      <c r="V5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X5" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD5" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="0">
+      <c r="K5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" t="s">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" t="s">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>50</v>
       </c>
-      <c r="AF5" s="0">
+      <c r="AF5">
         <v>20</v>
       </c>
-      <c r="AG5" s="0">
+      <c r="AG5">
         <v>40</v>
       </c>
-      <c r="AH5" s="0">
+      <c r="AH5">
         <v>15</v>
       </c>
-      <c r="AI5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ5" s="0" t="s">
+      <c r="AI5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>91</v>
       </c>
-      <c r="AK5" s="0" t="s">
+      <c r="AK5" t="s">
         <v>92</v>
       </c>
-      <c r="AM5" s="0">
+      <c r="AM5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="70.75" customHeight="1">
-      <c r="B6" s="0">
+    <row r="6" ht="70.75" customHeight="1" spans="1:39">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>101</v>
+      </c>
+      <c r="R6">
+        <v>15</v>
+      </c>
+      <c r="S6" t="s">
+        <v>102</v>
+      </c>
+      <c r="T6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U6">
+        <v>10</v>
+      </c>
+      <c r="V6" t="s">
+        <v>3</v>
+      </c>
+      <c r="W6" t="s">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>50</v>
+      </c>
+      <c r="AF6">
+        <v>20</v>
+      </c>
+      <c r="AG6">
+        <v>40</v>
+      </c>
+      <c r="AH6">
+        <v>15</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="70.75" customHeight="1" spans="1:39">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" t="s">
+        <v>99</v>
+      </c>
+      <c r="M7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7">
+        <v>15</v>
+      </c>
+      <c r="S7" t="s">
+        <v>100</v>
+      </c>
+      <c r="T7" t="s">
+        <v>101</v>
+      </c>
+      <c r="U7">
+        <v>20</v>
+      </c>
+      <c r="V7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>50</v>
+      </c>
+      <c r="AF7">
+        <v>20</v>
+      </c>
+      <c r="AG7">
+        <v>40</v>
+      </c>
+      <c r="AH7">
+        <v>15</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="42.75" customHeight="1" spans="1:39">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>50</v>
+      </c>
+      <c r="AF8">
+        <v>20</v>
+      </c>
+      <c r="AG8">
+        <v>40</v>
+      </c>
+      <c r="AH8">
+        <v>15</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AM8">
         <v>9</v>
       </c>
-      <c r="I6" s="0" t="s">
+    </row>
+    <row r="9" ht="42.75" customHeight="1" spans="1:39">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>50</v>
+      </c>
+      <c r="AF9">
+        <v>20</v>
+      </c>
+      <c r="AG9">
+        <v>40</v>
+      </c>
+      <c r="AH9">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" ht="42.75" customHeight="1" spans="1:39">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" t="s">
+        <v>99</v>
+      </c>
+      <c r="M10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>50</v>
+      </c>
+      <c r="AF10">
+        <v>20</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="42.75" customHeight="1" spans="1:39">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" t="s">
+        <v>99</v>
+      </c>
+      <c r="M11" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" t="s">
+        <v>3</v>
+      </c>
+      <c r="O11" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>3</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
+        <v>3</v>
+      </c>
+      <c r="T11" t="s">
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
+        <v>3</v>
+      </c>
+      <c r="W11" t="s">
+        <v>3</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>50</v>
+      </c>
+      <c r="AF11">
+        <v>20</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="56.75" customHeight="1" spans="1:39">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" t="s">
+        <v>99</v>
+      </c>
+      <c r="M12" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>50</v>
+      </c>
+      <c r="AF12">
+        <v>20</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>139</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:39">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H13">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" t="s">
+        <v>99</v>
+      </c>
+      <c r="M13" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>3</v>
+      </c>
+      <c r="T13" t="s">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>3</v>
+      </c>
+      <c r="W13" t="s">
+        <v>3</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>50</v>
+      </c>
+      <c r="AF13">
+        <v>20</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="42.75" customHeight="1" spans="1:39">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>50</v>
+      </c>
+      <c r="AF14">
+        <v>20</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="70.75" customHeight="1" spans="1:39">
+      <c r="B15">
+        <v>1000</v>
+      </c>
+      <c r="C15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" t="s">
+        <v>153</v>
+      </c>
+      <c r="H15">
+        <v>200</v>
+      </c>
+      <c r="I15" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J15" t="s">
         <v>98</v>
       </c>
-      <c r="K6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="0" t="s">
+      <c r="K15" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" t="s">
         <v>99</v>
       </c>
-      <c r="M6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" s="0" t="s">
+      <c r="M15" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" t="s">
         <v>100</v>
       </c>
-      <c r="Q6" s="0" t="s">
+      <c r="Q15" t="s">
         <v>101</v>
       </c>
-      <c r="R6" s="0">
-        <v>15</v>
-      </c>
-      <c r="S6" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="T6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U6" s="0">
+      <c r="R15">
         <v>10</v>
       </c>
-      <c r="V6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X6" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA6" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD6" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF6" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG6" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH6" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI6" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ6" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="AK6" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL6" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM6" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" ht="70.75" customHeight="1">
-      <c r="B7" s="0">
-        <v>3</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="0">
-        <v>9</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q7" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="R7" s="0">
-        <v>15</v>
-      </c>
-      <c r="S7" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="T7" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="U7" s="0">
-        <v>20</v>
-      </c>
-      <c r="V7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF7" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG7" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH7" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ7" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK7" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL7" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM7" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" ht="42.75" customHeight="1">
-      <c r="B8" s="0">
-        <v>4</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="H8" s="0">
-        <v>6</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="0">
-        <v>0</v>
-      </c>
-      <c r="S8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="0">
-        <v>0</v>
-      </c>
-      <c r="V8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD8" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF8" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG8" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH8" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ8" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="AK8" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL8" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="AM8" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" ht="42.75" customHeight="1">
-      <c r="B9" s="0">
-        <v>5</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="H9" s="0">
-        <v>6</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="0">
-        <v>0</v>
-      </c>
-      <c r="S9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="0">
-        <v>0</v>
-      </c>
-      <c r="V9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X9" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF9" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG9" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH9" s="0">
-        <v>15</v>
-      </c>
-      <c r="AI9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ9" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="AK9" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL9" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="AM9" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" customHeight="1">
-      <c r="B10" s="0">
-        <v>6</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="H10" s="0">
-        <v>6</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="0">
-        <v>0</v>
-      </c>
-      <c r="S10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="0">
-        <v>0</v>
-      </c>
-      <c r="V10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X10" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF10" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK10" s="0" t="s">
+      <c r="S15" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL15" t="s">
         <v>129</v>
       </c>
-      <c r="AL10" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="AM10" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" ht="42.75" customHeight="1">
-      <c r="B11" s="0">
-        <v>7</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="0">
-        <v>6</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J11" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R11" s="0">
-        <v>0</v>
-      </c>
-      <c r="S11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U11" s="0">
-        <v>0</v>
-      </c>
-      <c r="V11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X11" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF11" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK11" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL11" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM11" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" ht="56.75" customHeight="1">
-      <c r="B12" s="0">
-        <v>8</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="H12" s="0">
-        <v>6</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J12" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="0">
-        <v>0</v>
-      </c>
-      <c r="S12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="0">
-        <v>0</v>
-      </c>
-      <c r="V12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X12" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF12" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK12" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL12" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM12" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="B13" s="0">
-        <v>9</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="0">
-        <v>6</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R13" s="0">
-        <v>0</v>
-      </c>
-      <c r="S13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U13" s="0">
-        <v>0</v>
-      </c>
-      <c r="V13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X13" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF13" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK13" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="AL13" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM13" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="42.75" customHeight="1">
-      <c r="B14" s="0">
-        <v>10</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="H14" s="0">
-        <v>6</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="0">
-        <v>0</v>
-      </c>
-      <c r="S14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="0">
-        <v>0</v>
-      </c>
-      <c r="V14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF14" s="0">
-        <v>20</v>
-      </c>
-      <c r="AG14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL14" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="AM14" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" ht="70.75" customHeight="1">
-      <c r="B15" s="0">
-        <v>1000</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="H15" s="0">
-        <v>200</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="J15" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="M15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="R15" s="0">
-        <v>10</v>
-      </c>
-      <c r="S15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="0">
-        <v>0</v>
-      </c>
-      <c r="V15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="X15" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL15" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM15" s="0">
+      <c r="AM15">
         <v>8</v>
       </c>
     </row>
